--- a/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 15,57</t>
+          <t>-23,12; 16,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 39,63</t>
+          <t>-6,95; 43,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 19,26</t>
+          <t>-17,88; 20,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 9,93</t>
+          <t>-17,96; 9,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 22,68</t>
+          <t>-12,16; 24,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 5,38</t>
+          <t>-21,41; 4,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 9,1</t>
+          <t>-14,59; 7,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 25,96</t>
+          <t>-2,82; 25,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 8,59</t>
+          <t>-12,91; 8,14</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,32; —</t>
+          <t>-50,31; 1053,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,14; —</t>
+          <t>-80,78; 531,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,39; 817,06</t>
+          <t>-80,74; 791,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 171,64</t>
+          <t>-78,03; 143,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 541,2</t>
+          <t>-25,42; 395,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 184,83</t>
+          <t>-74,36; 171,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,04; -1,8</t>
+          <t>-34,43; -2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 3,66</t>
+          <t>-30,9; 5,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 4,59</t>
+          <t>-31,31; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 19,89</t>
+          <t>-14,72; 20,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 9,53</t>
+          <t>-21,15; 9,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 33,51</t>
+          <t>-9,55; 33,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 1,1</t>
+          <t>-21,48; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 3,0</t>
+          <t>-19,86; 2,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 13,19</t>
+          <t>-13,85; 12,9</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-92,9; 36,91</t>
+          <t>-100,0; 70,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,64</t>
+          <t>-100,0; 177,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 247,11</t>
+          <t>-70,62; 234,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 12,3</t>
+          <t>-22,28; 12,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 13,49</t>
+          <t>-27,38; 12,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 37,83</t>
+          <t>-11,45; 41,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -6,3</t>
+          <t>-45,56; -7,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 17,97</t>
+          <t>-36,65; 18,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -6,93</t>
+          <t>-45,82; -6,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -4,86</t>
+          <t>-33,03; -3,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 7,39</t>
+          <t>-26,56; 8,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 2,29</t>
+          <t>-29,93; 1,72</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,29</t>
+          <t>-100,0; 0,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,46; 92,63</t>
+          <t>-86,45; 103,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,2</t>
+          <t>-100,0; 4,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,08</t>
+          <t>-100,0; -0,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 62,51</t>
+          <t>-85,63; 64,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-91,04; 27,68</t>
+          <t>-91,52; 36,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 15,57</t>
+          <t>-7,19; 16,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 10,03</t>
+          <t>-11,61; 11,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 4,78</t>
+          <t>-17,22; 4,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 14,8</t>
+          <t>-10,41; 14,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 26,78</t>
+          <t>-3,56; 28,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,88; -0,28</t>
+          <t>-20,86; -0,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 12,35</t>
+          <t>-5,68; 11,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 13,55</t>
+          <t>-4,46; 13,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -0,45</t>
+          <t>-14,77; -0,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 391,0</t>
+          <t>-49,69; 410,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,95; 327,01</t>
+          <t>-75,75; 312,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,08; 133,33</t>
+          <t>-99,49; 104,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 170,38</t>
+          <t>-49,95; 167,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 289,5</t>
+          <t>-19,39; 383,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,05; 11,76</t>
+          <t>-90,27; 27,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 168,74</t>
+          <t>-33,91; 142,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 168,88</t>
+          <t>-30,28; 163,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,56; -0,44</t>
+          <t>-85,47; -2,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 20,04</t>
+          <t>-17,32; 19,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 19,51</t>
+          <t>-21,21; 17,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 9,13</t>
+          <t>-25,77; 11,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 20,12</t>
+          <t>-3,99; 21,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 0,0</t>
+          <t>-17,68; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 27,97</t>
+          <t>-1,07; 26,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 16,24</t>
+          <t>-6,82; 15,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 8,75</t>
+          <t>-12,83; 8,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 15,8</t>
+          <t>-9,13; 14,87</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,4; 319,82</t>
+          <t>-65,87; 349,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 271,25</t>
+          <t>-72,95; 252,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,05; 170,62</t>
+          <t>-84,74; 198,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-84,88; —</t>
+          <t>-72,65; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,1; —</t>
+          <t>-47,99; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 321,99</t>
+          <t>-46,1; 258,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 155,48</t>
+          <t>-79,26; 147,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,65; 289,88</t>
+          <t>-53,73; 293,6</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-75,41; -18,91</t>
+          <t>-75,39; -18,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 3,42</t>
+          <t>-61,93; 3,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-74,67; -13,44</t>
+          <t>-73,78; -10,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 2,41</t>
+          <t>-47,65; 3,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 25,91</t>
+          <t>-34,58; 29,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 17,98</t>
+          <t>-40,04; 19,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-50,37; -10,67</t>
+          <t>-53,94; -13,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 6,74</t>
+          <t>-40,46; 5,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-46,67; -4,33</t>
+          <t>-44,47; -3,39</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-92,97; 48,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 35,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 205,02</t>
+          <t>-85,95; 312,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-98,74; 202,11</t>
+          <t>-88,31; 224,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,03</t>
+          <t>-100,0; -12,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 37,72</t>
+          <t>-82,42; 37,56</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-93,09; 14,69</t>
+          <t>-92,11; 3,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 3,35</t>
+          <t>-11,17; 3,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 6,53</t>
+          <t>-9,08; 6,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 0,19</t>
+          <t>-15,09; -0,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 3,19</t>
+          <t>-10,37; 3,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 6,62</t>
+          <t>-9,5; 6,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 1,19</t>
+          <t>-12,48; 1,33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 1,07</t>
+          <t>-8,75; 1,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,55</t>
+          <t>-6,54; 4,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -1,46</t>
+          <t>-11,26; -1,44</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-58,15; 32,2</t>
+          <t>-55,68; 35,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 56,94</t>
+          <t>-47,08; 55,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-71,03; 2,86</t>
+          <t>-71,47; -3,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 26,6</t>
+          <t>-53,55; 27,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 50,82</t>
+          <t>-48,97; 53,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 9,52</t>
+          <t>-61,74; 15,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 8,47</t>
+          <t>-46,59; 13,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 34,74</t>
+          <t>-35,95; 35,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -9,92</t>
+          <t>-60,42; -9,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 16,03</t>
+          <t>-22,42; 14,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 43,38</t>
+          <t>-9,98; 40,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 20,19</t>
+          <t>-17,25; 19,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 9,8</t>
+          <t>-17,14; 10,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 24,35</t>
+          <t>-11,81; 22,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 4,71</t>
+          <t>-20,62; 6,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 7,84</t>
+          <t>-14,04; 8,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 25,37</t>
+          <t>-3,61; 26,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 8,14</t>
+          <t>-14,41; 8,9</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 1053,13</t>
+          <t>-62,17; 774,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,78; 531,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,74; 791,07</t>
+          <t>-81,18; 660,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,03; 143,93</t>
+          <t>-74,12; 190,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 395,08</t>
+          <t>-28,07; 466,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,36; 171,38</t>
+          <t>-78,78; 183,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -2,46</t>
+          <t>-33,55; -2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 5,96</t>
+          <t>-30,42; 5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 3,38</t>
+          <t>-30,39; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 20,85</t>
+          <t>-15,86; 18,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 9,41</t>
+          <t>-20,29; 9,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 33,61</t>
+          <t>-6,63; 33,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 1,24</t>
+          <t>-20,95; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 2,51</t>
+          <t>-21,15; 2,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 12,9</t>
+          <t>-14,17; 12,14</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 283,84</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,08</t>
+          <t>-94,0; 59,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 177,37</t>
+          <t>-100,0; 109,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 234,83</t>
+          <t>-75,03; 163,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 12,61</t>
+          <t>-21,04; 12,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 12,7</t>
+          <t>-21,58; 12,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 41,41</t>
+          <t>-12,09; 37,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,56; -7,69</t>
+          <t>-46,9; -5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 18,03</t>
+          <t>-36,53; 15,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,82; -6,93</t>
+          <t>-47,0; -7,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,03; -3,22</t>
+          <t>-32,95; -3,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 8,73</t>
+          <t>-28,35; 6,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 1,72</t>
+          <t>-31,14; 1,45</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,78</t>
+          <t>-100,0; 66,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,45; 103,38</t>
+          <t>-85,65; 88,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,84</t>
+          <t>-100,0; 4,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,48</t>
+          <t>-100,0; 15,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,63; 64,51</t>
+          <t>-89,18; 50,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 36,55</t>
+          <t>-100,0; 21,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 16,31</t>
+          <t>-6,39; 16,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 11,03</t>
+          <t>-11,05; 10,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 4,52</t>
+          <t>-16,13; 4,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 14,07</t>
+          <t>-11,08; 13,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 28,22</t>
+          <t>-4,36; 24,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,86; -0,54</t>
+          <t>-21,79; -1,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 11,45</t>
+          <t>-5,18; 11,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 13,69</t>
+          <t>-3,96; 14,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -0,22</t>
+          <t>-15,05; -0,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 410,58</t>
+          <t>-52,32; 450,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 312,11</t>
+          <t>-77,6; 280,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-99,49; 104,05</t>
+          <t>-94,36; 129,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 167,16</t>
+          <t>-49,75; 188,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 383,12</t>
+          <t>-26,62; 273,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,27; 27,91</t>
+          <t>-92,6; 17,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 142,17</t>
+          <t>-31,32; 143,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 163,49</t>
+          <t>-26,59; 176,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-85,47; -2,28</t>
+          <t>-86,11; 2,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 19,2</t>
+          <t>-20,63; 17,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 17,94</t>
+          <t>-20,75; 18,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 11,7</t>
+          <t>-26,05; 10,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 21,36</t>
+          <t>-3,99; 19,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 0,0</t>
+          <t>-16,43; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 26,47</t>
+          <t>-0,53; 28,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 15,95</t>
+          <t>-6,9; 15,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 8,0</t>
+          <t>-12,82; 7,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 14,87</t>
+          <t>-7,14; 14,62</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,87; 349,43</t>
+          <t>-73,14; 252,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 252,45</t>
+          <t>-75,91; 304,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 198,06</t>
+          <t>-83,33; 226,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,65; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,99; —</t>
+          <t>-45,51; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 258,37</t>
+          <t>-46,08; 261,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-79,26; 147,06</t>
+          <t>-79,56; 126,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 293,6</t>
+          <t>-47,8; 253,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-75,39; -18,7</t>
+          <t>-75,34; -19,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 3,78</t>
+          <t>-65,37; 5,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-73,78; -10,63</t>
+          <t>-74,49; -14,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 3,28</t>
+          <t>-46,42; 2,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 29,65</t>
+          <t>-33,31; 28,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 19,64</t>
+          <t>-41,17; 16,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-53,94; -13,28</t>
+          <t>-51,95; -12,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 5,77</t>
+          <t>-40,62; 6,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -3,39</t>
+          <t>-45,11; -4,14</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 68,92</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 31,51</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-83,32; 230,36</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 35,68</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-85,95; 312,19</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-88,31; 224,65</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,54</t>
+          <t>-100,0; -11,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 37,56</t>
+          <t>-81,57; 40,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-92,11; 3,39</t>
+          <t>-89,82; 5,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 3,41</t>
+          <t>-11,43; 2,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 6,28</t>
+          <t>-8,83; 6,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,09; -0,63</t>
+          <t>-14,58; -0,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 3,21</t>
+          <t>-10,33; 3,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 6,53</t>
+          <t>-8,75; 6,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 1,33</t>
+          <t>-12,06; 1,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,51</t>
+          <t>-8,75; 0,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,54</t>
+          <t>-7,02; 4,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -1,44</t>
+          <t>-11,21; -1,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 35,14</t>
+          <t>-58,33; 27,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 55,18</t>
+          <t>-45,41; 61,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-71,47; -3,58</t>
+          <t>-72,38; 1,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 27,53</t>
+          <t>-52,46; 24,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 53,75</t>
+          <t>-45,98; 52,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 15,17</t>
+          <t>-60,51; 10,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 13,54</t>
+          <t>-46,69; 6,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 35,38</t>
+          <t>-37,11; 30,66</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-60,42; -9,63</t>
+          <t>-60,15; -11,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,08</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16,08</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 14,08</t>
+          <t>-19,55; 9,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 40,88</t>
+          <t>-11,89; 22,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 19,35</t>
+          <t>-21,26; 4,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 10,13</t>
+          <t>-23,18; 15,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 22,87</t>
+          <t>-8,57; 39,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 6,06</t>
+          <t>-19,34; 20,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 8,83</t>
+          <t>-14,39; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 26,16</t>
+          <t>-3,5; 25,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 8,9</t>
+          <t>-13,77; 9,2</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-34,52%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-58,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-7,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>116,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-34,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>47,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-54,23%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-15,43%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 774,71</t>
+          <t>-81,39; 817,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 660,23</t>
+          <t>-54,32; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,52; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 190,7</t>
+          <t>-80,66; 171,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 466,9</t>
+          <t>-30,82; 541,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 183,07</t>
+          <t>-75,85; 195,77</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,83</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-15,78</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-13,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-11,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,83</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,27</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-33,55; -2,13</t>
+          <t>-15,65; 19,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 5,31</t>
+          <t>-18,65; 9,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 4,49</t>
+          <t>-7,59; 36,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 18,9</t>
+          <t>-34,04; -1,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 9,64</t>
+          <t>-30,59; 3,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 33,95</t>
+          <t>-29,38; 6,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 0,81</t>
+          <t>-19,11; 1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 2,28</t>
+          <t>-20,35; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 12,14</t>
+          <t>-13,5; 15,23</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-44,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>133,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-85,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-71,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-64,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-44,76%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>119,91%</t>
+          <t>-60,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,33%</t>
+          <t>-1,13%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,0; 59,15</t>
+          <t>-92,9; 36,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 109,07</t>
+          <t>-100,0; 133,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 163,55</t>
+          <t>-69,76; 266,59</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-26,8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-12,99</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-26,33</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,88</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-26,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,99</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-27,32</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,77</t>
+          <t>-13,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 12,75</t>
+          <t>-46,55; -6,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 12,98</t>
+          <t>-36,6; 17,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 37,76</t>
+          <t>-44,59; -3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,9; -5,45</t>
+          <t>-22,11; 12,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 15,79</t>
+          <t>-21,88; 13,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -7,42</t>
+          <t>-7,59; 39,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,95; -3,33</t>
+          <t>-33,45; -4,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 6,03</t>
+          <t>-28,12; 7,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 1,45</t>
+          <t>-29,27; 5,02</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-81,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,68%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-80,43%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-14,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-12,1%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>128,65%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-81,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-39,68%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-83,45%</t>
+          <t>143,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-61,1%</t>
+          <t>-55,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 39,29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-88,46; 92,63</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 23,65</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 66,07</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-85,65; 88,21</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 4,31</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,72</t>
+          <t>-100,0; -2,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 50,52</t>
+          <t>-88,3; 62,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,5</t>
+          <t>-89,83; 45,23</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-9,96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,31</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,28</t>
+          <t>-5,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 16,68</t>
+          <t>-11,85; 14,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 10,97</t>
+          <t>-3,47; 26,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 4,69</t>
+          <t>-21,59; 0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 13,99</t>
+          <t>-7,71; 15,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 24,64</t>
+          <t>-10,86; 10,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,79; -1,01</t>
+          <t>-11,16; 11,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 11,98</t>
+          <t>-4,55; 12,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 14,1</t>
+          <t>-4,55; 13,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -0,17</t>
+          <t>-12,74; 2,47</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-65,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>50,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-45,53%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>70,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-66,74%</t>
+          <t>-0,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-58,69%</t>
+          <t>-41,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 450,95</t>
+          <t>-50,64; 170,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 280,43</t>
+          <t>-26,94; 289,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,36; 129,41</t>
+          <t>-90,4; 18,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 188,8</t>
+          <t>-55,4; 391,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 273,72</t>
+          <t>-71,95; 327,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,6; 17,36</t>
+          <t>-77,8; 416,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 143,4</t>
+          <t>-29,17; 168,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 176,69</t>
+          <t>-29,04; 168,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,11; 2,94</t>
+          <t>-74,92; 41,5</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,11</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-5,39</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,85</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-5,39</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>-6,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>2,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 17,96</t>
+          <t>-4,62; 20,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 18,66</t>
+          <t>-18,15; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 10,13</t>
+          <t>-2,79; 23,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 19,99</t>
+          <t>-17,48; 20,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 0,0</t>
+          <t>-20,4; 19,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 28,08</t>
+          <t>-25,33; 9,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 15,64</t>
+          <t>-6,19; 16,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 7,29</t>
+          <t>-11,41; 8,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 14,62</t>
+          <t>-8,13; 13,35</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>131,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>182,73%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-1,44%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-35,37%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>131,87%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>220,22%</t>
+          <t>-34,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 252,33</t>
+          <t>-84,88; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 304,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,33; 226,71</t>
+          <t>-52,04; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-65,4; 319,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,32; 271,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,51; —</t>
+          <t>-86,24; 205,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 261,35</t>
+          <t>-39,28; 321,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 126,83</t>
+          <t>-73,86; 155,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 253,42</t>
+          <t>-52,7; 243,55</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-21,9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,64</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-8,82</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-48,05</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-30,96</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-43,45</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-21,9</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-5,64</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,12</t>
+          <t>-43,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-24,59</t>
+          <t>-23,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-75,34; -19,52</t>
+          <t>-47,63; 2,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 5,6</t>
+          <t>-35,95; 25,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-74,49; -14,4</t>
+          <t>-36,83; 21,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 2,66</t>
+          <t>-75,41; -18,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 28,52</t>
+          <t>-64,67; 3,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 16,95</t>
+          <t>-74,66; -13,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-51,95; -12,49</t>
+          <t>-50,37; -10,67</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 6,88</t>
+          <t>-38,02; 6,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-45,11; -4,14</t>
+          <t>-45,58; -3,38</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-75,43%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-19,41%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-30,37%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-64,45%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-90,43%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-75,43%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-19,41%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-38,28%</t>
+          <t>-90,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-67,19%</t>
+          <t>-64,62%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,92</t>
+          <t>-100,0; 205,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,51</t>
+          <t>-100,0; 217,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-92,97; 48,4</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-83,32; 230,36</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,11</t>
+          <t>-100,0; -18,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 40,22</t>
+          <t>-79,32; 37,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-89,82; 5,19</t>
+          <t>-92,17; 24,05</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-3,84</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,26</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,44</t>
+          <t>-4,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,25</t>
+          <t>-4,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,58</t>
+          <t>-11,26; 3,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,74</t>
+          <t>-8,87; 6,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -0,02</t>
+          <t>-12,12; 1,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 3,11</t>
+          <t>-11,2; 3,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 6,14</t>
+          <t>-9,4; 6,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1,15</t>
+          <t>-11,73; 3,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 0,86</t>
+          <t>-8,69; 1,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,08</t>
+          <t>-6,6; 4,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -1,47</t>
+          <t>-9,79; -0,21</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-22,1%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-9,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-33,53%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-24,6%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-8,08%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-45,26%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-22,1%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-9,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-34,37%</t>
+          <t>-29,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-39,76%</t>
+          <t>-31,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-58,33; 27,27</t>
+          <t>-57,41; 26,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 61,97</t>
+          <t>-47,19; 50,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 1,85</t>
+          <t>-60,63; 14,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 24,29</t>
+          <t>-58,15; 32,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 52,35</t>
+          <t>-47,86; 56,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 10,97</t>
+          <t>-58,76; 31,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 6,58</t>
+          <t>-47,57; 8,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 30,66</t>
+          <t>-36,32; 34,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-60,15; -11,35</t>
+          <t>-51,98; -0,43</t>
         </is>
       </c>
     </row>
